--- a/artfynd/A 14221-2026 artfynd.xlsx
+++ b/artfynd/A 14221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114128287</v>
+        <v>114128612</v>
       </c>
       <c r="B2" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -730,7 +725,7 @@
         <v>824221</v>
       </c>
       <c r="R2" t="n">
-        <v>7300608</v>
+        <v>7300606</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -794,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114128612</v>
+        <v>114128287</v>
       </c>
       <c r="B3" t="n">
-        <v>56720</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,7 +826,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -849,7 +839,7 @@
         <v>824221</v>
       </c>
       <c r="R3" t="n">
-        <v>7300606</v>
+        <v>7300608</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -910,6 +900,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114569686</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>824208</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7300460</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Andrea Lindberg, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14221-2026 artfynd.xlsx
+++ b/artfynd/A 14221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114128612</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114128287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569686</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>